--- a/source/Autossential.Workbook.Tests/Samples/OXML_sheets.xlsx
+++ b/source/Autossential.Workbook.Tests/Samples/OXML_sheets.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <x:workbookPr/>
   <x:bookViews>
-    <x:workbookView windowWidth="28800" windowHeight="12435"/>
+    <x:workbookView windowWidth="28800" windowHeight="12300" activeTab="3"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,17 +12,30 @@
     <x:sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <x:sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </x:sheets>
-  <x:calcPr calcId="144525"/>
+  <x:calcPr calcId="191029"/>
+  <x:extLst>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </x:ext>
+  </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -33,30 +46,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -64,45 +64,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -116,6 +77,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -134,19 +103,27 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -157,6 +134,21 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -164,6 +156,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -172,6 +171,20 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -186,187 +199,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,30 +390,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -438,6 +427,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -452,17 +456,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -482,148 +495,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -635,52 +648,52 @@
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="40% - Ênfase 4" xfId="3" builtinId="43"/>
-    <cellStyle name="Porcentagem" xfId="4" builtinId="5"/>
-    <cellStyle name="Célula Vinculada" xfId="5" builtinId="24"/>
-    <cellStyle name="Célula de Verificação" xfId="6" builtinId="23"/>
-    <cellStyle name="Moeda [0]" xfId="7" builtinId="7"/>
-    <cellStyle name="20% - Ênfase 3" xfId="8" builtinId="38"/>
-    <cellStyle name="Moeda" xfId="9" builtinId="4"/>
-    <cellStyle name="Hyperlink seguido" xfId="10" builtinId="9"/>
-    <cellStyle name="Hyperlink" xfId="11" builtinId="8"/>
-    <cellStyle name="40% - Ênfase 2" xfId="12" builtinId="35"/>
-    <cellStyle name="Observação" xfId="13" builtinId="10"/>
-    <cellStyle name="40% - Ênfase 6" xfId="14" builtinId="51"/>
-    <cellStyle name="Texto de Aviso" xfId="15" builtinId="11"/>
-    <cellStyle name="Título" xfId="16" builtinId="15"/>
-    <cellStyle name="Texto Explicativo" xfId="17" builtinId="53"/>
-    <cellStyle name="Ênfase 3" xfId="18" builtinId="37"/>
-    <cellStyle name="Título 1" xfId="19" builtinId="16"/>
-    <cellStyle name="Ênfase 4" xfId="20" builtinId="41"/>
-    <cellStyle name="Título 2" xfId="21" builtinId="17"/>
-    <cellStyle name="Ênfase 5" xfId="22" builtinId="45"/>
-    <cellStyle name="Título 3" xfId="23" builtinId="18"/>
-    <cellStyle name="Ênfase 6" xfId="24" builtinId="49"/>
-    <cellStyle name="Título 4" xfId="25" builtinId="19"/>
-    <cellStyle name="Entrada" xfId="26" builtinId="20"/>
-    <cellStyle name="Saída" xfId="27" builtinId="21"/>
-    <cellStyle name="Cálculo" xfId="28" builtinId="22"/>
-    <cellStyle name="Total" xfId="29" builtinId="25"/>
-    <cellStyle name="40% - Ênfase 1" xfId="30" builtinId="31"/>
-    <cellStyle name="Bom" xfId="31" builtinId="26"/>
-    <cellStyle name="Ruim" xfId="32" builtinId="27"/>
-    <cellStyle name="Neutro" xfId="33" builtinId="28"/>
-    <cellStyle name="20% - Ênfase 5" xfId="34" builtinId="46"/>
-    <cellStyle name="Ênfase 1" xfId="35" builtinId="29"/>
-    <cellStyle name="20% - Ênfase 1" xfId="36" builtinId="30"/>
-    <cellStyle name="60% - Ênfase 1" xfId="37" builtinId="32"/>
-    <cellStyle name="20% - Ênfase 6" xfId="38" builtinId="50"/>
-    <cellStyle name="Ênfase 2" xfId="39" builtinId="33"/>
-    <cellStyle name="20% - Ênfase 2" xfId="40" builtinId="34"/>
-    <cellStyle name="60% - Ênfase 2" xfId="41" builtinId="36"/>
-    <cellStyle name="40% - Ênfase 3" xfId="42" builtinId="39"/>
-    <cellStyle name="60% - Ênfase 3" xfId="43" builtinId="40"/>
-    <cellStyle name="20% - Ênfase 4" xfId="44" builtinId="42"/>
-    <cellStyle name="60% - Ênfase 4" xfId="45" builtinId="44"/>
-    <cellStyle name="40% - Ênfase 5" xfId="46" builtinId="47"/>
-    <cellStyle name="60% - Ênfase 5" xfId="47" builtinId="48"/>
+    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
+    <cellStyle name="Porcentagem" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Moeda [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Hyperlink seguido" xfId="7" builtinId="9"/>
+    <cellStyle name="Observação" xfId="8" builtinId="10"/>
+    <cellStyle name="Texto de Aviso" xfId="9" builtinId="11"/>
+    <cellStyle name="Título" xfId="10" builtinId="15"/>
+    <cellStyle name="Texto Explicativo" xfId="11" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
+    <cellStyle name="Saída" xfId="17" builtinId="21"/>
+    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
+    <cellStyle name="Célula de Verificação" xfId="19" builtinId="23"/>
+    <cellStyle name="Célula Vinculada" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Bom" xfId="22" builtinId="26"/>
+    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
+    <cellStyle name="Ênfase 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Ênfase 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Ênfase 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Ênfase 1" xfId="28" builtinId="32"/>
+    <cellStyle name="Ênfase 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Ênfase 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Ênfase 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Ênfase 2" xfId="32" builtinId="36"/>
+    <cellStyle name="Ênfase 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Ênfase 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Ênfase 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Ênfase 3" xfId="36" builtinId="40"/>
+    <cellStyle name="Ênfase 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Ênfase 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Ênfase 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Ênfase 4" xfId="40" builtinId="44"/>
+    <cellStyle name="Ênfase 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Ênfase 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Ênfase 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Ênfase 5" xfId="44" builtinId="48"/>
+    <cellStyle name="Ênfase 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Ênfase 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Ênfase 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Ênfase 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>

--- a/source/Autossential.Workbook.Tests/Samples/OXML_sheets.xlsx
+++ b/source/Autossential.Workbook.Tests/Samples/OXML_sheets.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <x:workbookPr/>
   <x:bookViews>
